--- a/docs/publications/close-2025/auditors-report.xlsx
+++ b/docs/publications/close-2025/auditors-report.xlsx
@@ -489,7 +489,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:38 UTC</t>
+          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:38 UTC</t>
+          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:38 UTC</t>
+          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:38 UTC</t>
+          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:38 UTC</t>
+          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/publications/close-2025/auditors-report.xlsx
+++ b/docs/publications/close-2025/auditors-report.xlsx
@@ -40,10 +40,10 @@
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,17 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,510 +486,510 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
+          <t>Period 2025 · prepared 2026-09-17 09:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>CERTIFIED — Tom Metzinger, 15 Sep 2026.</t>
+          <t>REHEARSAL — NOT CERTIFIED. A drive produced this signature to prove the mechanism; no person gave it.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>The signature records what was unfinished when it was given, and those steps are part of it: The paper behind the judgments, The position on each invoice.</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Nothing resting on it may be sent to a sponsor. The rate itself is arithmetic and stands; what is missing is somebody putting their name to it.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>All cross-reference points tie.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Classification is 100.0% complete by dollars. Unclassified cost sits in no pool and is never defaulted into one, so any rate below reads high while the queue is open — which is the honest direction to err.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Asset register: OPEN.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>What it proves</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Ledger side</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Statement side</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Ties</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>PL_FOOTING</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Profit and loss foots to the net income the sheet carries</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>P&amp;L sections</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="6" t="n">
         <v>4329.28</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Balance sheet net income</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="6" t="n">
         <v>4329.28</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I13" s="6" t="b">
+      <c r="I13" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>BS_FOOTING</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Balance sheet balances</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="6" t="n">
         <v>16713219.8</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Liabilities and equity</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="6" t="n">
         <v>16713219.8</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I14" s="6" t="b">
+      <c r="I14" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>GL_PROMOTE_COMPLETE</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Every staged line reached the ledger</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Dated lines staged</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="6" t="n">
         <v>15500</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Lines in the ledger</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="6" t="n">
         <v>15500</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I15" s="6" t="b">
+      <c r="I15" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>GL_SUBTOTALS</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Printed account totals agree with the parsed lines</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Printed</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="6" t="n">
         <v>14371299.3</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Parsed</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="6" t="n">
         <v>14371299.3</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I16" s="6" t="b">
+      <c r="I16" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>GL_PL_SECTION</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Ledger P&amp;L-scope activity agrees with the P&amp;L by section</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Ledger</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="6" t="n">
         <v>13554753.64</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>P&amp;L</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="6" t="n">
         <v>13554753.64</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I17" s="6" t="b">
+      <c r="I17" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>GL_PL_ACCOUNT</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Ledger agrees with the P&amp;L account by account</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Gross difference</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="6" t="n">
         <v>14939.74</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Left unexplained</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="6" t="n">
         <v>14939.74</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I18" s="6" t="b">
+      <c r="I18" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>GL_PL_COVERAGE</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Every P&amp;L account exists on both sides</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Ledger accounts absent from the P&amp;L</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>P&amp;L accounts with no ledger lines</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I19" s="6" t="b">
+      <c r="I19" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>GL_BS_ACCOUNT</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Opening balance plus the year's movement equals the sheet</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Accounts tied</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Accounts off</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I20" s="6" t="b">
+      <c r="I20" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>GL_BS_COVERAGE</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Accounts absent from the sheet closed at zero</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Absent, closing at zero</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Absent, carrying a balance</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I21" s="6" t="b">
+      <c r="I21" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>SEGMENTATION</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Split lines still sum to the lines they came from</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Ledger</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>14371299.3</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Analytical</t>
         </is>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>14371299.3</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I22" s="6" t="b">
+      <c r="I22" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>PAYROLL_REGISTER</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>The payroll register agrees with the ledger's wage accounts</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Register</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>1835047.17</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Ledger wage accounts</t>
         </is>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="6" t="n">
         <v>1789993.94</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>TIES</t>
         </is>
       </c>
-      <c r="I23" s="6" t="b">
+      <c r="I23" s="5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1037,275 +1034,275 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
+          <t>Period 2025 · prepared 2026-09-17 09:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Ledger puts it in</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>The statement puts it in</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Lines</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Recorded by</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>GL_PL_ACCOUNT</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Grant Expenses:Rising Tides Expense</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Program Expenses:ESP</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="6" t="n">
         <v>6300</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>RECLASS_AFTER_EXPORT</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>tom@ybi.org</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>3 lines sitting in Grant Expenses:Rising Tides Expense in the general ledger and in Program Expenses:ESP on the profit and loss. The two exports are two moments in the same books; the reclassification was posted after the ledger was run. No effect on the section total or net income.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>GL_PL_ACCOUNT</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Grant Expenses:Rising Tides Expense</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Management &amp; Administrative Expenses:5205 Travel:5206 Travel</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="6" t="n">
         <v>622.26</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>RECLASS_AFTER_EXPORT</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>tom@ybi.org</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>4 lines sitting in Grant Expenses:Rising Tides Expense in the general ledger and in Management &amp; Administrative Expenses:5205 Travel:5206 Travel on the profit and loss. The two exports are two moments in the same books; the reclassification was posted after the ledger was run. No effect on the section total or net income.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>GL_PL_ACCOUNT</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Grant Expenses:Rising Tides Expense</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>5080 Fundraising:5085 Advertising</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="6" t="n">
         <v>280.4</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>RECLASS_AFTER_EXPORT</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>tom@ybi.org</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>1 line sitting in Grant Expenses:Rising Tides Expense in the general ledger and in 5080 Fundraising:5085 Advertising on the profit and loss. The two exports are two moments in the same books; the reclassification was posted after the ledger was run. No effect on the section total or net income.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>GL_PL_ACCOUNT</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Grant Expenses:Rising Tides Expense</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Management &amp; Administrative Expenses:5300 Staff Training - Education</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="6" t="n">
         <v>267.21</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>RECLASS_AFTER_EXPORT</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>tom@ybi.org</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>2 lines sitting in Grant Expenses:Rising Tides Expense in the general ledger and in Management &amp; Administrative Expenses:5300 Staff Training - Education on the profit and loss. The two exports are two moments in the same books; the reclassification was posted after the ledger was run. No effect on the section total or net income.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>PAYROLL_REGISTER</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>5129 Payroll Expenses:5139 Wages:5142 Intern Wages</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>4000 Contributions Income</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="6" t="n">
         <v>-45000</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>SOURCE_DEFECT</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>tom@ybi.org</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>A pledge from Vince and Phyllis Bacon to fund interns, booked as a credit against intern wage expense instead of as contribution income. The same donor's September gift went to 4029 Sponsorships correctly, so this is a misposting rather than a policy. It understates both contributions and wages by $45,000 on the Form 990, and understates the fringe base by 2.5% — which is the whole of the difference between a 21.90% and a 22.45% reading of the fringe rate.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>PAYROLL_REGISTER</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>5129 Payroll Expenses:5139 Wages:5142 Intern Wages</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>register</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>-53.23</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>ROUNDING</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>tom@ybi.org</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>53.23 on a 1,835,047.17 base — three thousandths of one per cent — with no transaction behind it. The controller's workbook distributes dollars across 43 people and sixteen objectives and rounds each cell; no single line accounts for it, and none can be named.</t>
         </is>
@@ -1348,115 +1345,115 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
+          <t>Period 2025 · prepared 2026-09-17 09:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Pool</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Dollars</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Documented</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>% documented</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="6" t="n">
         <v>4368588.09</v>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="6" t="n">
         <v>2919689</v>
       </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>OVERHEAD</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="6" t="n">
         <v>1765875.34</v>
       </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>FRINGE</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="6" t="n">
         <v>461144.62</v>
       </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>FUNDRAISING</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="6" t="n">
         <v>281753.41</v>
       </c>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>G&amp;A</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="6" t="n">
         <v>266098.29</v>
       </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>UNALLOWABLE</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="6" t="n">
         <v>117493.35</v>
       </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1498,42 +1495,42 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
+          <t>Period 2025 · prepared 2026-09-17 09:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Who</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>When</t>
         </is>
@@ -1580,191 +1577,191 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
+          <t>Period 2025 · prepared 2026-09-17 09:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Pool</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Base amount</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Sealed by</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Seal</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>FRINGE</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="6" t="n">
         <v>401783.6</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>SALARIES_WAGES</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="6" t="n">
         <v>1835047.17</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="7" t="n">
         <v>0.219</v>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>60fb3f4b52219514d8f0dc8d20c962ad2fd902dee0cf2407da91f2a93d215a37</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>G&amp;A</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="6" t="n">
         <v>585875.91</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>MTDC</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="6" t="n">
         <v>4736602.11</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="7" t="n">
         <v>0.1237</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>60fb3f4b52219514d8f0dc8d20c962ad2fd902dee0cf2407da91f2a93d215a37</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>INDIRECT_COMBINED</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="6" t="n">
         <v>1170650.43</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>MTDC</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="6" t="n">
         <v>4736602.11</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>0.2471</v>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>60fb3f4b52219514d8f0dc8d20c962ad2fd902dee0cf2407da91f2a93d215a37</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>OVERHEAD</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="6" t="n">
         <v>584774.52</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>MTDC</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="6" t="n">
         <v>4736602.11</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="7" t="n">
         <v>0.1235</v>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>60fb3f4b52219514d8f0dc8d20c962ad2fd902dee0cf2407da91f2a93d215a37</t>
         </is>
